--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -8,25 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="Final" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="17">
   <si>
     <t>Docente</t>
   </si>
   <si>
+    <t>Mat</t>
+  </si>
+  <si>
     <t>Grupo</t>
   </si>
   <si>
-    <t>Mat</t>
-  </si>
-  <si>
     <t>Totales</t>
   </si>
   <si>
@@ -36,10 +35,10 @@
     <t>Reprobados</t>
   </si>
   <si>
-    <t>Por_Apro</t>
-  </si>
-  <si>
-    <t>Por_Repro</t>
+    <t>por_aprobados</t>
+  </si>
+  <si>
+    <t>por_reprobados</t>
   </si>
   <si>
     <t>Promedio</t>
@@ -48,22 +47,25 @@
     <t>Blancos</t>
   </si>
   <si>
-    <t>Por_Blan</t>
+    <t>por_blancos</t>
   </si>
   <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>INTRODUCCIÓN A LA ECONOMÍA</t>
+  </si>
+  <si>
+    <t>TEMAS DE ADMINISTRACIÓN</t>
+  </si>
+  <si>
     <t>6ARHM</t>
   </si>
   <si>
     <t>6ARHV</t>
-  </si>
-  <si>
-    <t>INTRODUCCIÓN A LA ECONOMÍA</t>
-  </si>
-  <si>
-    <t>TEMAS DE ADMINISTRACIÓN</t>
   </si>
 </sst>
 </file>
@@ -427,11 +429,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -477,10 +479,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -512,7 +514,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -550,7 +552,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -582,10 +584,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -609,6 +611,64 @@
         <v>0</v>
       </c>
       <c r="K5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>132</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>132</v>
+      </c>
+      <c r="E7">
+        <v>132</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -619,11 +679,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -669,31 +729,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.5</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -701,7 +764,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -710,22 +773,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.5</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -736,28 +802,31 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8.1</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -765,204 +834,15 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>100</v>
-      </c>
-      <c r="J5">
-        <v>30</v>
-      </c>
-      <c r="K5" s="1">
-        <v>100</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="1"/>
-    <col min="9" max="9" width="9.140625" style="2"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2">
-        <v>36</v>
-      </c>
-      <c r="E2">
-        <v>36</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>36</v>
-      </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>30</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
         <v>30</v>
       </c>
       <c r="F5">
@@ -981,6 +861,64 @@
         <v>0</v>
       </c>
       <c r="K5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>132</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>132</v>
+      </c>
+      <c r="E7">
+        <v>132</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="18">
   <si>
     <t>Docente</t>
   </si>
@@ -53,13 +53,16 @@
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>INTRODUCCIÓN A LA ECONOMÍA</t>
   </si>
   <si>
     <t>TEMAS DE ADMINISTRACIÓN</t>
+  </si>
+  <si>
+    <t>Totales Docente</t>
+  </si>
+  <si>
+    <t>Totales Generales</t>
   </si>
   <si>
     <t>6ARHM</t>
@@ -433,7 +436,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -479,10 +482,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -514,10 +517,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>36</v>
@@ -549,10 +552,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -584,10 +587,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -618,6 +621,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
       <c r="D6">
         <v>132</v>
       </c>
@@ -644,8 +650,8 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="D7">
         <v>132</v>
@@ -729,10 +735,10 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>36</v>
@@ -764,10 +770,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>36</v>
@@ -799,10 +805,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>30</v>
@@ -834,10 +840,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>30</v>
@@ -868,6 +874,9 @@
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
       <c r="D6">
         <v>132</v>
       </c>
@@ -894,8 +903,8 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
+      <c r="B7" t="s">
+        <v>15</v>
       </c>
       <c r="D7">
         <v>132</v>

--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
-    <sheet name="Final" sheetId="2" r:id="rId2"/>
+    <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="18">
   <si>
     <t>Docente</t>
   </si>
@@ -744,6 +745,259 @@
         <v>36</v>
       </c>
       <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1">
+        <v>100</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>36</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1">
+        <v>100</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>36</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>100</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>30</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>132</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>132</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>132</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>132</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>132</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2">
         <v>36</v>
       </c>
       <c r="F2">

--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -745,25 +745,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -780,25 +780,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -882,25 +882,25 @@
         <v>132</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F6">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J6">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -911,25 +911,25 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F7">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>54.5</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>45.5</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J3">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -815,25 +815,25 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -850,25 +850,25 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -882,25 +882,25 @@
         <v>132</v>
       </c>
       <c r="E6">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J6">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -911,25 +911,25 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="F7">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J7">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20222.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20222.xlsx
@@ -689,8 +689,7 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -942,8 +941,7 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="1" max="2" width="30.7109375" customWidth="1"/>
     <col min="7" max="8" width="9.140625" style="1"/>
     <col min="9" max="9" width="9.140625" style="2"/>
     <col min="11" max="11" width="9.140625" style="1"/>
@@ -1010,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1045,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1080,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1115,7 +1113,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1147,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1176,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
         <v>0</v>
